--- a/Preliminary Data/two forces (15 trials)(tapered and cylindrical)/Validation(2.00to1.25)(3tendon).xlsx
+++ b/Preliminary Data/two forces (15 trials)(tapered and cylindrical)/Validation(2.00to1.25)(3tendon).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/SoRoSim Robots/my_robot(2.00to1.25)(3tendon)/10-08-2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Bio-Inspired-Sensing/Preliminary Data/two forces (15 trials)(tapered and cylindrical)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2869" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DCBC7EC-7605-4723-BE47-7319270BC215}"/>
+  <xr:revisionPtr revIDLastSave="2870" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C9289A3-45BE-44C4-AE92-A97713F7FE58}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (double)" sheetId="12" r:id="rId1"/>
@@ -515,6 +515,9 @@
     <xf numFmtId="164" fontId="4" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -525,6 +528,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -540,21 +555,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -922,68 +922,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B763EDC-8536-442D-A8D3-F37978D4DE80}">
   <dimension ref="A1:AC18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="7.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="23" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="25" t="s">
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="27" t="s">
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="29"/>
-    </row>
-    <row r="2" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="34"/>
+    </row>
+    <row r="2" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>0.3</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>-0.16968383775705329</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>0.4</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>6.9846011870356717E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>0.7</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>-3.5774078873262199E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>0.7</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>-0.11738587778127019</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>0.6</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>-1.8520203450577422E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>0.8</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>-5.542594283105548E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>0.3</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>5.8475902526015949E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>0.5</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>7.2511475698173899E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>0.4</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>1.4258336355669421E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>0.7</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>0.11017490691826692</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>0.3</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>2.6205596248324969E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>0.6</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>8.753144830914783E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>0.7</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>-0.12862977834001521</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>0.4</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>6.9869847527751716E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>0.8</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>-1.6577221491043369E-2</v>
       </c>
       <c r="AA17" s="5">
-        <f t="shared" si="6"/>
+        <f>O17-U17</f>
         <v>-7.2552709906399726E-2</v>
       </c>
       <c r="AB17" s="5">
@@ -2527,7 +2527,7 @@
         <v>5.6870872849057119E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
       <c r="X18" s="17">
         <f>AVERAGE(X4:X17)</f>
         <v>-1.5408713342843674E-3</v>
@@ -2569,101 +2569,101 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309BE333-3BAE-4E8D-AF02-67A9E2013036}">
   <dimension ref="A1:AS17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
-    <col min="27" max="27" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7265625" customWidth="1"/>
+    <col min="27" max="27" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.7265625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="23" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="33" t="s">
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="31" t="s">
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="AB1" s="31"/>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="31"/>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="32" t="s">
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="32"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-    </row>
-    <row r="2" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="29"/>
+      <c r="AM1" s="29"/>
+      <c r="AN1" s="29"/>
+      <c r="AO1" s="29"/>
+      <c r="AP1" s="29"/>
+      <c r="AQ1" s="29"/>
+      <c r="AR1" s="29"/>
+      <c r="AS1" s="29"/>
+    </row>
+    <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -2775,18 +2775,18 @@
       <c r="AK2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="AL2" s="30" t="s">
+      <c r="AL2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-    </row>
-    <row r="3" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM2" s="21"/>
+      <c r="AN2" s="21"/>
+      <c r="AO2" s="21"/>
+      <c r="AP2" s="21"/>
+      <c r="AQ2" s="21"/>
+      <c r="AR2" s="21"/>
+      <c r="AS2" s="21"/>
+    </row>
+    <row r="3" spans="1:45" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <f>'Proximal Validation (double)'!A3</f>
         <v>0.3</v>
@@ -2951,7 +2951,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <f>'Proximal Validation (double)'!A4</f>
         <v>0.4</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <f>'Proximal Validation (double)'!A5</f>
         <v>0.7</v>
@@ -3264,18 +3264,18 @@
         <f t="shared" si="8"/>
         <v>1.5996178598034261E-2</v>
       </c>
-      <c r="AL5" s="30" t="s">
+      <c r="AL5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="AM5" s="30"/>
-      <c r="AN5" s="30"/>
-      <c r="AO5" s="30"/>
-      <c r="AP5" s="30"/>
-      <c r="AQ5" s="30"/>
-      <c r="AR5" s="30"/>
-      <c r="AS5" s="30"/>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AM5" s="21"/>
+      <c r="AN5" s="21"/>
+      <c r="AO5" s="21"/>
+      <c r="AP5" s="21"/>
+      <c r="AQ5" s="21"/>
+      <c r="AR5" s="21"/>
+      <c r="AS5" s="21"/>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <f>'Proximal Validation (double)'!A6</f>
         <v>0.7</v>
@@ -3430,7 +3430,7 @@
       <c r="AR6" s="8"/>
       <c r="AS6" s="8"/>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <f>'Proximal Validation (double)'!A7</f>
         <v>0.6</v>
@@ -3588,7 +3588,7 @@
       <c r="AR7" s="8"/>
       <c r="AS7" s="8"/>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <f>'Proximal Validation (double)'!A8</f>
         <v>0.8</v>
@@ -3729,7 +3729,7 @@
         <v>0.3543173457748785</v>
       </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <f>'Proximal Validation (double)'!A9</f>
         <v>0.3</v>
@@ -3873,7 +3873,7 @@
       <c r="AM9" s="13"/>
       <c r="AN9" s="13"/>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <f>'Proximal Validation (double)'!A10</f>
         <v>0.5</v>
@@ -4014,7 +4014,7 @@
         <v>5.5551180786501675E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <f>'Proximal Validation (double)'!A11</f>
         <v>0.4</v>
@@ -4158,7 +4158,7 @@
       <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <f>'Proximal Validation (double)'!A12</f>
         <v>0.7</v>
@@ -4299,7 +4299,7 @@
         <v>8.6974061820051185E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <f>'Proximal Validation (double)'!A13</f>
         <v>0.3</v>
@@ -4443,7 +4443,7 @@
       <c r="AM13" s="13"/>
       <c r="AN13" s="13"/>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <f>'Proximal Validation (double)'!A14</f>
         <v>0.6</v>
@@ -4584,7 +4584,7 @@
         <v>2.4030642950857519</v>
       </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <f>'Proximal Validation (double)'!A15</f>
         <v>0.7</v>
@@ -4725,7 +4725,7 @@
         <v>0.4975500671542139</v>
       </c>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <f>'Proximal Validation (double)'!A16</f>
         <v>0.4</v>
@@ -4866,7 +4866,7 @@
         <v>0.6477108966008629</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <f>'Proximal Validation (double)'!A17</f>
         <v>0.8</v>
@@ -5025,101 +5025,101 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85518B9D-1727-46C0-A190-BB1F8B3D1295}">
   <dimension ref="A1:AS20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.7265625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="23" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="33" t="s">
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="31" t="s">
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="AB1" s="31"/>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="31"/>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="32" t="s">
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="32"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-    </row>
-    <row r="2" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="29"/>
+      <c r="AM1" s="29"/>
+      <c r="AN1" s="29"/>
+      <c r="AO1" s="29"/>
+      <c r="AP1" s="29"/>
+      <c r="AQ1" s="29"/>
+      <c r="AR1" s="29"/>
+      <c r="AS1" s="29"/>
+    </row>
+    <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -5231,18 +5231,18 @@
       <c r="AK2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="AL2" s="30" t="s">
+      <c r="AL2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-    </row>
-    <row r="3" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM2" s="21"/>
+      <c r="AN2" s="21"/>
+      <c r="AO2" s="21"/>
+      <c r="AP2" s="21"/>
+      <c r="AQ2" s="21"/>
+      <c r="AR2" s="21"/>
+      <c r="AS2" s="21"/>
+    </row>
+    <row r="3" spans="1:45" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>0.7</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>0.7</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>0.5</v>
       </c>
@@ -5678,18 +5678,18 @@
         <f t="shared" si="1"/>
         <v>2.0405258817366434E-3</v>
       </c>
-      <c r="AL5" s="30" t="s">
+      <c r="AL5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="AM5" s="30"/>
-      <c r="AN5" s="30"/>
-      <c r="AO5" s="30"/>
-      <c r="AP5" s="30"/>
-      <c r="AQ5" s="30"/>
-      <c r="AR5" s="30"/>
-      <c r="AS5" s="30"/>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AM5" s="21"/>
+      <c r="AN5" s="21"/>
+      <c r="AO5" s="21"/>
+      <c r="AP5" s="21"/>
+      <c r="AQ5" s="21"/>
+      <c r="AR5" s="21"/>
+      <c r="AS5" s="21"/>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>0.4</v>
       </c>
@@ -5830,7 +5830,7 @@
       <c r="AR6" s="8"/>
       <c r="AS6" s="8"/>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>0.6</v>
       </c>
@@ -5974,7 +5974,7 @@
       <c r="AR7" s="8"/>
       <c r="AS7" s="8"/>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>0.8</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>7.4018716234747206E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>0.3</v>
       </c>
@@ -6228,7 +6228,7 @@
         <v>1.0901306550227252E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>0.4</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>8.8889957195015246E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>0.4</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>1.1944354411402847E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>0.8</v>
       </c>
@@ -6609,7 +6609,7 @@
         <v>7.8147889608726206E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>0.3</v>
       </c>
@@ -6736,7 +6736,7 @@
         <v>8.4271581786743432E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>0.5</v>
       </c>
@@ -6863,7 +6863,7 @@
         <v>2.3631704739087711E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>0.4</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>1.6375648648314645E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>0.7</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>1.9449019234518694E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>0.7</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>1.4109036345664183E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" s="17"/>
@@ -7263,7 +7263,7 @@
       <c r="AJ18" s="13"/>
       <c r="AK18" s="13"/>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="AA19" s="19"/>
       <c r="AB19" s="19"/>
       <c r="AC19" s="19"/>
@@ -7273,7 +7273,7 @@
       <c r="AG19" s="19"/>
       <c r="AH19" s="19"/>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="AA20" s="19"/>
       <c r="AB20" s="19"/>
       <c r="AC20" s="19"/>
@@ -7301,101 +7301,101 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E14665A-07EC-419E-BE64-3182EF192487}">
   <dimension ref="A1:AS20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="8" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.7265625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="23" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="33" t="s">
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="31" t="s">
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="AB1" s="31"/>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="31"/>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="32" t="s">
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="32"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-    </row>
-    <row r="2" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="29"/>
+      <c r="AM1" s="29"/>
+      <c r="AN1" s="29"/>
+      <c r="AO1" s="29"/>
+      <c r="AP1" s="29"/>
+      <c r="AQ1" s="29"/>
+      <c r="AR1" s="29"/>
+      <c r="AS1" s="29"/>
+    </row>
+    <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -7507,18 +7507,18 @@
       <c r="AK2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="AL2" s="30" t="s">
+      <c r="AL2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-    </row>
-    <row r="3" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM2" s="21"/>
+      <c r="AN2" s="21"/>
+      <c r="AO2" s="21"/>
+      <c r="AP2" s="21"/>
+      <c r="AQ2" s="21"/>
+      <c r="AR2" s="21"/>
+      <c r="AS2" s="21"/>
+    </row>
+    <row r="3" spans="1:45" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>0.4</v>
       </c>
@@ -7666,7 +7666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>0.7</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>0.7</v>
       </c>
@@ -7945,18 +7945,18 @@
         <f t="shared" si="1"/>
         <v>8.700466958162334E-2</v>
       </c>
-      <c r="AL5" s="30" t="s">
+      <c r="AL5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="AM5" s="30"/>
-      <c r="AN5" s="30"/>
-      <c r="AO5" s="30"/>
-      <c r="AP5" s="30"/>
-      <c r="AQ5" s="30"/>
-      <c r="AR5" s="30"/>
-      <c r="AS5" s="30"/>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AM5" s="21"/>
+      <c r="AN5" s="21"/>
+      <c r="AO5" s="21"/>
+      <c r="AP5" s="21"/>
+      <c r="AQ5" s="21"/>
+      <c r="AR5" s="21"/>
+      <c r="AS5" s="21"/>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>0.8</v>
       </c>
@@ -8094,7 +8094,7 @@
       <c r="AR6" s="8"/>
       <c r="AS6" s="8"/>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -8150,7 +8150,7 @@
       <c r="AR7" s="8"/>
       <c r="AS7" s="8"/>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -8189,7 +8189,7 @@
       <c r="AJ8" s="9"/>
       <c r="AK8" s="9"/>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -8228,7 +8228,7 @@
       <c r="AJ9" s="9"/>
       <c r="AK9" s="9"/>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -8267,7 +8267,7 @@
       <c r="AJ10" s="9"/>
       <c r="AK10" s="9"/>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -8306,7 +8306,7 @@
       <c r="AJ11" s="9"/>
       <c r="AK11" s="9"/>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -8345,7 +8345,7 @@
       <c r="AJ12" s="9"/>
       <c r="AK12" s="9"/>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -8384,7 +8384,7 @@
       <c r="AJ13" s="10"/>
       <c r="AK13" s="10"/>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -8423,7 +8423,7 @@
       <c r="AJ14" s="9"/>
       <c r="AK14" s="9"/>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -8462,7 +8462,7 @@
       <c r="AJ15" s="9"/>
       <c r="AK15" s="9"/>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -8501,7 +8501,7 @@
       <c r="AJ16" s="9"/>
       <c r="AK16" s="9"/>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -8540,7 +8540,7 @@
       <c r="AJ17" s="9"/>
       <c r="AK17" s="9"/>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="AA18" s="19"/>
       <c r="AB18" s="19"/>
       <c r="AC18" s="19"/>
@@ -8553,7 +8553,7 @@
       <c r="AJ18" s="13"/>
       <c r="AK18" s="13"/>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="AA19" s="19"/>
       <c r="AB19" s="19"/>
       <c r="AC19" s="19"/>
@@ -8563,7 +8563,7 @@
       <c r="AG19" s="19"/>
       <c r="AH19" s="19"/>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="AA20" s="19"/>
       <c r="AB20" s="19"/>
       <c r="AC20" s="19"/>
@@ -8591,9 +8591,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC3D7D9-740E-4BB1-A5C5-EC42A3C8479B}">
   <dimension ref="A1:N39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>39</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B2" s="5">
         <v>0.7</v>
       </c>
@@ -8678,7 +8678,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B3" s="5">
         <v>0.5</v>
       </c>
@@ -8719,7 +8719,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B4" s="5">
         <v>0.4</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>0.6</v>
       </c>
@@ -8801,7 +8801,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B6" s="5">
         <v>0.8</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>0.3</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B8" s="5">
         <v>0.4</v>
       </c>
@@ -8924,7 +8924,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>0.4</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B10" s="5">
         <v>0.8</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>0.3</v>
       </c>
@@ -9047,7 +9047,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>0.5</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>0.4</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>0.7</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>0.7</v>
       </c>
@@ -9211,7 +9211,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>-2.7164795354451751E-14</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>1.0847210817916337E-6</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>-1.238702018106301E-14</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B22">
         <v>-1.7242899307191666E-14</v>
       </c>
@@ -9374,7 +9374,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>6.1334368644179289E-6</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>-2.1949623025118236E-14</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>-3.0608683479936208E-14</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B26">
         <v>-1.4075276669817153E-15</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>-1.2963779744525572E-14</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B28">
         <v>-4.5574354391758017E-7</v>
       </c>
@@ -9566,7 +9566,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B29">
         <v>-1.4551864836986917E-6</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B30">
         <v>-1.5336159361711936E-6</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B31">
         <v>-1.8829406105603694E-13</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B32">
         <v>-3.5374644164448377E-6</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="4:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:14" x14ac:dyDescent="0.35">
       <c r="D36" t="s">
         <v>39</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="4:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:14" x14ac:dyDescent="0.35">
       <c r="E37">
         <v>-1.1449491139501301E-3</v>
       </c>
@@ -9761,7 +9761,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="4:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:14" x14ac:dyDescent="0.35">
       <c r="E38">
         <v>-3.7175370380282402E-3</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="4:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:14" x14ac:dyDescent="0.35">
       <c r="E39">
         <v>-1.16670653223991E-2</v>
       </c>
@@ -9834,9 +9834,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="35" t="s">
         <v>21</v>
       </c>
@@ -9854,7 +9854,7 @@
       <c r="L1" s="36"/>
       <c r="M1" s="37"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.112474009394646</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>0.112474009394646</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>-3.05809658020735E-2</v>
       </c>
@@ -9980,7 +9980,7 @@
         <v>-3.05809658020735E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>-0.101423710584641</v>
       </c>
@@ -10024,7 +10024,7 @@
         <v>-0.101423710584641</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.27253100275993303</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>0.27253100275993303</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.20345818996429399</v>
       </c>
@@ -10112,7 +10112,7 @@
         <v>0.20345818996429399</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.14228719472885101</v>
       </c>
@@ -10156,7 +10156,7 @@
         <v>0.14228719472885101</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>-0.22458755970001201</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>-0.22458755970001201</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-0.42087453603744501</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>-0.42087453603744501</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-0.26614278554916398</v>
       </c>
@@ -10288,7 +10288,7 @@
         <v>-0.26614278554916398</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-0.85049569606780995</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>-0.85049569606780995</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-0.98430818319320701</v>
       </c>
@@ -10376,7 +10376,7 @@
         <v>-0.98430818319320701</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-0.62923872470855702</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>-0.62923872470855702</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-0.65422439575195301</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>-0.65422439575195301</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>-0.82157814502716098</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>-0.82157814502716098</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>-0.80446076393127397</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>-0.80446076393127397</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>-0.78086811304092396</v>
       </c>
@@ -10606,12 +10606,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10868,17 +10867,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10903,18 +10912,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>